--- a/paper_tables/Table_5_Top5_Actual_vs_Predicted_Summary.xlsx
+++ b/paper_tables/Table_5_Top5_Actual_vs_Predicted_Summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top5_Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 5 Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -89,16 +89,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,199 +465,419 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Act Eads (eV)</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Pred Eads (eV)</t>
+          <t>Chemical Family</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Act Eg (eV)</t>
+          <t>Composite Score</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Pred Eg (eV)</t>
+          <t>band_gap_DFT</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Act K (GPa)</t>
+          <t>band_gap_CGCNN</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Pred K (GPa)</t>
+          <t>formation_energy_DFT</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>formation_energy_CGCNN</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>energy_hull_DFT</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>energy_hull_CGCNN</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>E_ads_DFT_eV_DFT</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>E_ads_DFT_eV_CGCNN</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>bulk_modulus_DFT</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>bulk_modulus_CGCNN</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>shear_modulus_DFT</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>shear_modulus_CGCNN</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>young_modulus_DFT</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>young_modulus_CGCNN</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Carbides</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K2" s="2" t="n">
         <v>-2.83</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>-2.749</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>3.536</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>3.637</v>
-      </c>
-      <c r="F2" s="3" t="n">
+      <c r="L2" s="2" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>419.28</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>416.498</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>0.762</v>
+      <c r="N2" s="2" t="n">
+        <v>422.6</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>475.47</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>476.2</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1035.13</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1036.04</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>FeOF</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>-2.047</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>-2.046</v>
-      </c>
-      <c r="D3" s="5" t="n">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>NbC</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Carbides</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="5" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>172.31</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>164.278</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>0.648</v>
+      <c r="F3" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>299.63</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>303.13</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>195.56</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>200.94</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>481.85</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>484.77</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>NbC</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>-1.78</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>-1.759</v>
-      </c>
-      <c r="D4" s="3" t="n">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>FeOF</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>299.63</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>305.343</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>0.621</v>
+      <c r="F4" s="2" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>172.31</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>173.28</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>88.58</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>230.94</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>241.4</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>NbF3</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>-3.058</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>-3.031</v>
-      </c>
-      <c r="D5" s="5" t="n">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Rb2F</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>95.03</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>98.117</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>0.593</v>
+      <c r="F5" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>10.2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Rb2F</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>-2.035</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>-2.078</v>
-      </c>
-      <c r="D6" s="3" t="n">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>CuMoO4</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>10.71</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>8.215999999999999</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0.592</v>
+      <c r="F6" s="2" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>131.37</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>133.69</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>158.2</v>
       </c>
     </row>
   </sheetData>
